--- a/jpcore-r4/feature/wg45-FamilyMember/StructureDefinition-jp-familymemberhistory-siblingorder.xlsx
+++ b/jpcore-r4/feature/wg45-FamilyMember/StructureDefinition-jp-familymemberhistory-siblingorder.xlsx
@@ -135,7 +135,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:FamilyMemberHistory</t>
+    <t>element:FamilyMemberHistory.relationship</t>
   </si>
   <si>
     <t>ID</t>
